--- a/data/cabelos_iaf.xlsx
+++ b/data/cabelos_iaf.xlsx
@@ -344,7 +344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1036"/>
+  <dimension ref="A1:C1038"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.421875" customWidth="1" min="1" max="1"/>
@@ -15894,6 +15894,40 @@
         </is>
       </c>
     </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>94200</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>MATCH MASC C H 2AB 3AB CIEN/CURV V2 350g</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>89784</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>MALBEC COND TRAT ANTICASPA CUID V4 250ml</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1028"/>
   <printOptions headings="0" gridLines="0"/>

--- a/data/cabelos_iaf.xlsx
+++ b/data/cabelos_iaf.xlsx
@@ -344,7 +344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1038"/>
+  <dimension ref="A1:C1039"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.421875" customWidth="1" min="1" max="1"/>
@@ -15928,6 +15928,23 @@
         </is>
       </c>
     </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>oBoticário</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>98399</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>COMBO MATCH</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1028"/>
   <printOptions headings="0" gridLines="0"/>

--- a/data/cabelos_iaf.xlsx
+++ b/data/cabelos_iaf.xlsx
@@ -344,7 +344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1039"/>
+  <dimension ref="A1:C1040"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.421875" customWidth="1" min="1" max="1"/>
@@ -15945,6 +15945,23 @@
         </is>
       </c>
     </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>Eudora</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>89383</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>ESTJ SIAGE PRO CRONOLOGY MAES/26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1028"/>
   <printOptions headings="0" gridLines="0"/>
